--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24640,7 +24640,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25042,7 +25042,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25846,7 +25846,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26798,7 +26798,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27602,7 +27602,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28956,7 +28956,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32468,7 +32468,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33272,7 +33272,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34224,7 +34224,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34626,7 +34626,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -35028,7 +35028,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35578,7 +35578,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35980,7 +35980,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36382,7 +36382,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37334,7 +37334,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37736,7 +37736,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38138,7 +38138,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38540,7 +38540,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38942,7 +38942,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39492,7 +39492,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40296,7 +40296,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40698,7 +40698,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41248,7 +41248,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41650,7 +41650,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -42052,7 +42052,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42454,7 +42454,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42856,7 +42856,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43808,7 +43808,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44210,7 +44210,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45162,7 +45162,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45966,7 +45966,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46368,7 +46368,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46918,7 +46918,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47320,7 +47320,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47722,7 +47722,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48124,7 +48124,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48526,7 +48526,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49076,7 +49076,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49478,7 +49478,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49880,7 +49880,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50282,7 +50282,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50832,7 +50832,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51234,7 +51234,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51636,7 +51636,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -52038,7 +52038,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52990,7 +52990,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53392,7 +53392,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53794,7 +53794,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54196,7 +54196,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54746,7 +54746,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55148,7 +55148,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55550,7 +55550,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55952,7 +55952,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24640,7 +24640,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25042,7 +25042,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25846,7 +25846,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26798,7 +26798,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27602,7 +27602,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28956,7 +28956,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32468,7 +32468,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33272,7 +33272,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34224,7 +34224,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34626,7 +34626,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -35028,7 +35028,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35578,7 +35578,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35980,7 +35980,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36382,7 +36382,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37334,7 +37334,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37736,7 +37736,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38138,7 +38138,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38540,7 +38540,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38942,7 +38942,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39492,7 +39492,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40296,7 +40296,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40698,7 +40698,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41248,7 +41248,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41650,7 +41650,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -42052,7 +42052,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42454,7 +42454,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42856,7 +42856,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43808,7 +43808,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44210,7 +44210,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45162,7 +45162,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45966,7 +45966,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46368,7 +46368,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46918,7 +46918,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47320,7 +47320,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47722,7 +47722,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48124,7 +48124,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48526,7 +48526,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49076,7 +49076,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49478,7 +49478,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49880,7 +49880,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50282,7 +50282,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50832,7 +50832,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51234,7 +51234,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51636,7 +51636,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -52038,7 +52038,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52990,7 +52990,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53392,7 +53392,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53794,7 +53794,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54196,7 +54196,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54746,7 +54746,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55148,7 +55148,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55550,7 +55550,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55952,7 +55952,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1061,9 +1055,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1200,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1357,9 +1345,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1505,9 +1490,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1635,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1801,9 +1780,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1925,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2097,9 +2070,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2245,9 +2215,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2360,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2541,9 +2505,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2650,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2837,9 +2795,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2940,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3085,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3281,9 +3230,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3429,9 +3375,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3520,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3725,9 +3665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4128,7 +4065,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -4530,7 +4467,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -4932,7 +4869,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -5079,9 +5016,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5482,7 +5416,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -5884,7 +5818,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6286,7 +6220,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -6688,7 +6622,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -6835,9 +6769,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7238,7 +7169,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -7640,7 +7571,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -8042,7 +7973,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -8444,7 +8375,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -8591,9 +8522,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8994,7 +8922,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9396,7 +9324,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -9798,7 +9726,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10200,7 +10128,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10602,7 +10530,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -10749,9 +10677,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11152,7 +11077,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -11554,7 +11479,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -11956,7 +11881,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -12358,7 +12283,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -12505,9 +12430,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12908,7 +12830,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13310,7 +13232,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -13712,7 +13634,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -14114,7 +14036,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -14261,9 +14183,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14664,7 +14583,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -15066,7 +14985,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -15468,7 +15387,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -15870,7 +15789,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -16272,7 +16191,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -16419,9 +16338,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -16822,7 +16738,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -17224,7 +17140,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -17626,7 +17542,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18028,7 +17944,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -18175,9 +18091,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -18578,7 +18491,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -18980,7 +18893,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -19382,7 +19295,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -19784,7 +19697,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -19931,9 +19844,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -20334,7 +20244,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -20736,7 +20646,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -21138,7 +21048,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -21540,7 +21450,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -21942,7 +21852,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -22089,9 +21999,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -22492,7 +22399,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -22894,7 +22801,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -23296,7 +23203,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -23698,7 +23605,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -23845,9 +23752,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -24248,7 +24152,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -24650,7 +24554,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -25052,7 +24956,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -25454,7 +25358,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -25856,7 +25760,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -26003,9 +25907,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -26406,7 +26307,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -26808,7 +26709,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -27210,7 +27111,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -27612,7 +27513,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -27759,9 +27660,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -28162,7 +28060,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -28564,7 +28462,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -28966,7 +28864,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -29368,7 +29266,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -29515,9 +29413,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -29918,7 +29813,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -30320,7 +30215,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -30722,7 +30617,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -31124,7 +31019,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -31526,7 +31421,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -31673,9 +31568,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -32076,7 +31968,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -32478,7 +32370,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -32880,7 +32772,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -33282,7 +33174,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -33429,9 +33321,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -33832,7 +33721,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -34234,7 +34123,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -34636,7 +34525,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -35038,7 +34927,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -35185,9 +35074,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -35588,7 +35474,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -35990,7 +35876,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -36392,7 +36278,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -36794,7 +36680,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -36941,9 +36827,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -37344,7 +37227,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -37746,7 +37629,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -38148,7 +38031,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -38550,7 +38433,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -38952,7 +38835,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -39099,9 +38982,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -39502,7 +39382,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -39904,7 +39784,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -40306,7 +40186,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -40708,7 +40588,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -40855,9 +40735,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -41258,7 +41135,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -41660,7 +41537,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -42062,7 +41939,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -42464,7 +42341,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -42866,7 +42743,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -43013,9 +42890,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -43416,7 +43290,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -43818,7 +43692,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -44220,7 +44094,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -44622,7 +44496,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -44769,9 +44643,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -45172,7 +45043,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -45574,7 +45445,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -45976,7 +45847,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -46378,7 +46249,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -46525,9 +46396,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -46928,7 +46796,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -47330,7 +47198,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -47732,7 +47600,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -48134,7 +48002,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -48536,7 +48404,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -48683,9 +48551,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -49086,7 +48951,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN254" t="b">
@@ -49488,7 +49353,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -49890,7 +49755,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -50292,7 +50157,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -50439,9 +50304,6 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -50842,7 +50704,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -51244,7 +51106,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -51646,7 +51508,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -52048,7 +51910,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -52195,9 +52057,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -52598,7 +52457,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -53000,7 +52859,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -53402,7 +53261,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -53804,7 +53663,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -54206,7 +54065,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -54353,9 +54212,6 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
@@ -54756,7 +54612,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -55158,7 +55014,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -55560,7 +55416,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -55962,7 +55818,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN289" t="b">

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18481,7 +18481,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24946,7 +24946,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29256,7 +29256,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29803,7 +29803,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30607,7 +30607,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31958,7 +31958,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32762,7 +32762,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33164,7 +33164,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35866,7 +35866,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36268,7 +36268,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36670,7 +36670,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37217,7 +37217,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37619,7 +37619,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38825,7 +38825,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39774,7 +39774,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40176,7 +40176,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40578,7 +40578,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41527,7 +41527,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -41929,7 +41929,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42331,7 +42331,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43280,7 +43280,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43682,7 +43682,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44084,7 +44084,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45033,7 +45033,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45435,7 +45435,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45837,7 +45837,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46239,7 +46239,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46786,7 +46786,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47188,7 +47188,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47590,7 +47590,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -47992,7 +47992,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48394,7 +48394,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48941,7 +48941,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49343,7 +49343,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49745,7 +49745,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50147,7 +50147,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50694,7 +50694,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51096,7 +51096,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51498,7 +51498,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51900,7 +51900,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52447,7 +52447,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52849,7 +52849,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53653,7 +53653,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55004,7 +55004,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55406,7 +55406,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55808,7 +55808,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18481,7 +18481,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24946,7 +24946,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29256,7 +29256,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29803,7 +29803,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30607,7 +30607,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31958,7 +31958,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32762,7 +32762,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33164,7 +33164,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35866,7 +35866,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36268,7 +36268,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36670,7 +36670,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37217,7 +37217,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37619,7 +37619,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38825,7 +38825,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39774,7 +39774,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40176,7 +40176,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40578,7 +40578,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41527,7 +41527,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -41929,7 +41929,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42331,7 +42331,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43280,7 +43280,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43682,7 +43682,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44084,7 +44084,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45033,7 +45033,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45435,7 +45435,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45837,7 +45837,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46239,7 +46239,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46786,7 +46786,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47188,7 +47188,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47590,7 +47590,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -47992,7 +47992,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48394,7 +48394,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48941,7 +48941,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49343,7 +49343,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49745,7 +49745,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50147,7 +50147,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50694,7 +50694,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51096,7 +51096,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51498,7 +51498,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51900,7 +51900,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52447,7 +52447,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52849,7 +52849,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53653,7 +53653,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55004,7 +55004,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55406,7 +55406,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55808,7 +55808,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18481,7 +18481,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24946,7 +24946,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29256,7 +29256,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29803,7 +29803,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30607,7 +30607,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31958,7 +31958,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32762,7 +32762,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33164,7 +33164,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35866,7 +35866,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36268,7 +36268,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36670,7 +36670,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37217,7 +37217,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37619,7 +37619,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38825,7 +38825,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39774,7 +39774,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40176,7 +40176,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40578,7 +40578,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41527,7 +41527,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -41929,7 +41929,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42331,7 +42331,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43280,7 +43280,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43682,7 +43682,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44084,7 +44084,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45033,7 +45033,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45435,7 +45435,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45837,7 +45837,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46239,7 +46239,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46786,7 +46786,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47188,7 +47188,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47590,7 +47590,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -47992,7 +47992,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48394,7 +48394,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48941,7 +48941,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49343,7 +49343,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49745,7 +49745,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50147,7 +50147,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50694,7 +50694,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51096,7 +51096,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51498,7 +51498,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51900,7 +51900,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52447,7 +52447,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52849,7 +52849,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53653,7 +53653,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55004,7 +55004,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55406,7 +55406,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55808,7 +55808,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d204/2010-2014.xlsx
+++ b/diseases/d204/2010-2014.xlsx
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18481,7 +18481,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18883,7 +18883,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22791,7 +22791,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24946,7 +24946,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29256,7 +29256,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29803,7 +29803,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30607,7 +30607,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31958,7 +31958,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32762,7 +32762,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33164,7 +33164,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35866,7 +35866,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36268,7 +36268,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36670,7 +36670,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37217,7 +37217,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37619,7 +37619,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38825,7 +38825,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39372,7 +39372,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39774,7 +39774,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40176,7 +40176,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40578,7 +40578,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41527,7 +41527,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -41929,7 +41929,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42331,7 +42331,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43280,7 +43280,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43682,7 +43682,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44084,7 +44084,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45033,7 +45033,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45435,7 +45435,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45837,7 +45837,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46239,7 +46239,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46786,7 +46786,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47188,7 +47188,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47590,7 +47590,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -47992,7 +47992,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48394,7 +48394,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48941,7 +48941,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49343,7 +49343,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49745,7 +49745,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50147,7 +50147,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50694,7 +50694,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51096,7 +51096,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51498,7 +51498,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51900,7 +51900,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52447,7 +52447,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52849,7 +52849,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53653,7 +53653,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55004,7 +55004,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55406,7 +55406,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55808,7 +55808,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
